--- a/fixtures/company_data/dennis_data.xlsx
+++ b/fixtures/company_data/dennis_data.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Latest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshot" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +32,22 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00F2F2EF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010331F"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,9 +62,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,642 +431,1229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>group</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — data · latest snapshot (formulas pre-filled)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>company_name</t>
+          <t>Ticker / RIC -&gt;</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Example Corp</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>EXMPL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>identity</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>field_key</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Value (auto)</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Field mnemonic (verify)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Identity</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Example Corp</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TR.CommonName</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ticker / RIC</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EXMPL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Exchange</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NASDAQ Global Select Market</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TR.ExchangeName</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GICS Sector</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TR.GICSSector</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Industry</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Application Software</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>TR.GICSIndustry</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>TR.HeadquartersCountry</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Reporting Currency</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TR.FinancialCurrency</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
         <is>
           <t>as_of_date</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>As-of Date</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>identity</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>market_cap</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>30700000000</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>shares_outstanding</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>364600000</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>enterprise_value</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>31900000000</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>size</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>revenue_ttm</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>496000000</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>growth</t>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>revenue_yoy_pct</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
+          <t>Price &amp; Size</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TR.PriceClose</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>revenue_cagr_3y_pct</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>4.2</v>
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>market_cap</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>growth</t>
+          <t>Market Cap</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>30700000000</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TR.CompanyMarketCap</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>gross_margin_pct</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>58</v>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>margins</t>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>31900000000</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TR.EV</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>operating_margin_pct</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-12</v>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shares_out</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>margins</t>
+          <t>Shares Outstanding</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>364600000</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>TR.SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Required</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>net_margin_pct</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-18</v>
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>avg_volume_3m</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>margins</t>
+          <t>Avg Daily Volume (3m)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>TR.AvgDailyVolume3M</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>net_income_ttm</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-89000000</v>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>margins</t>
+          <t>Beta (5y)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>TR.Beta</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>operating_cf_ttm</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>-9000000</v>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>week52_high</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>52-Week High</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>TR.Price52WeekHigh</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>capex_ttm</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>6000000</v>
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>week52_low</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>52-Week Low</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>TR.Price52WeekLow</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>fcf_ttm</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>-15000000</v>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>pct_from_52w_high</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>% From 52w High</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>-29.83</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fcf_margin_pct</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>-3</v>
+          <t>Valuation (now)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>pe_ttm</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>P/E (TTM)</t>
+        </is>
+      </c>
+      <c r="D22" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>TR.PE</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>fcf_yield_pct</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>-3</v>
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>forward_pe</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="D23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>TR.FwdPE</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cash_and_equivalents</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>410000000</v>
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ps_ttm</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>P/S (TTM)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>62</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>TR.PriceToSalesPerShare</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>total_debt</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1450000000</v>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ev_ebitda</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>EV / EBITDA</t>
+        </is>
+      </c>
+      <c r="D25" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>TR.EVToEBITDA</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>net_debt</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1040000000</v>
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ev_sales</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>EV / Sales</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>TR.EVToSales</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>net_debt_to_ebitda</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>9.800000000000001</v>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ev_fcf</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>EV / FCF</t>
+        </is>
+      </c>
+      <c r="D27" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TR.EVToFCF</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>debt_to_equity</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>140</v>
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>pb</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>P / B</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>18</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>TR.PriceToBVPerShare</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>interest_coverage</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.9</v>
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>p_fcf</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>balance</t>
+          <t>P / FCF</t>
+        </is>
+      </c>
+      <c r="D29" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>TR.PriceToFCFPerShare</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>roic_pct</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>-6.5</v>
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>peg</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>returns</t>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="D30" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>TR.PEG</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>roe_pct</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>-14</v>
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>earnings_yield</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>returns</t>
+          <t>Earnings Yield (%)</t>
+        </is>
+      </c>
+      <c r="D31" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="B32" t="e">
-        <v>#N/A</v>
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fcf_yield</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>FCF Yield (%)</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TR.FCFYield</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>ps_ratio</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>62</v>
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>dividend_yield</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>Dividend Yield (%)</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>TR.DividendYield</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>ev_ebitda</t>
-        </is>
-      </c>
-      <c r="B34" t="e">
-        <v>#N/A</v>
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>buyback_yield</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>Buyback Yield (%)</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>TR.BuybackYield</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>18</v>
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>shareholder_yield</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>valuation</t>
+          <t>Shareholder Yield (%)</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>p_fcf</t>
-        </is>
-      </c>
-      <c r="B36" t="e">
+          <t>Balance (now)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>cash_st</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cash &amp; ST Investments</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>TR.CashAndSTInvestments</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>total_debt_now</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1450000000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>TR.TotalDebtOutstanding</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>net_debt_now</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1040000000</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>net_debt_ebitda_now</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Net Debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>TR.NetDebtToEBITDA</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>debt_to_equity</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Debt / Equity (%)</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>140</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>TR.TotalDebtToTotalEquityPct</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>current_ratio</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Current Ratio</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>TR.CurrentRatio</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>quick_ratio</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Quick Ratio</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TR.QuickRatio</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Interest Coverage</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>TR.InterestCoverageRatio</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>goodwill_intang</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="D44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>valuation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>shares_outstanding_yoy_pct</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>6</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>dilution</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>buyback_yield_pct</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>short_interest_pct</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TR.GoodwillGross</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tangible_bv</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tangible BV / Share</t>
+        </is>
+      </c>
+      <c r="D45" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TR.TangibleBVPerShare</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Ownership &amp; Risk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>short_interest</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Short Interest (% float)</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>11</v>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>https://www.example.com</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>optional</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TR.ShortInterestPercentOfFloat</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>insider_own</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Insider Ownership (%)</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>8</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>TR.InsiderPercentHeld</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>institutional_own</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Institutional Own (%)</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>62</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TR.InstitutionsPercentHeld</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Recommended</t>
         </is>
       </c>
     </row>
@@ -1068,218 +1668,1448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FY2025</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — financial history (6 periods) + trend (formulas pre-filled)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>field_key</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>FY-4</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>FY-0</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>CAGR FY-4-&gt;FY-0 %</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Field mnemonic (verify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>471000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>491000000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>gross_profit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>252000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>280000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>287000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>288000000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>288000000</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>63</v>
+      </c>
+      <c r="D7" t="n">
+        <v>62</v>
+      </c>
+      <c r="E7" t="n">
+        <v>61</v>
+      </c>
+      <c r="F7" t="n">
+        <v>59</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58</v>
+      </c>
+      <c r="H7" t="n">
+        <v>58</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>operating_income</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-38000000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-49000000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-60000000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-60000000</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>operating_margin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operating Margin %</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-5000000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-20000000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-35000000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-45000000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-45000000</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-49000000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-70000000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-89000000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-89000000</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>net_margin</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-10.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-18</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>operating_cf</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fcf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-6000000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-15000000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-15000000</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fcf_margin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>FCF Margin %</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sbc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Stock-Based Comp</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>95000000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cash &amp; Equivalents</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>700000000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>610000000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>520000000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>465000000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>total_debt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>900000000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1350000000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1450000000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1450000000</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>net_debt</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>440000000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>680000000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>885000000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1040000000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1040000000</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>total_equity</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1150000000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1080000000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1030000000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1036000000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1036000000</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>roic</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ROIC %</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-3.6</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>diluted_shares</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Diluted Shares</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>298000000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>315000000</v>
+      </c>
+      <c r="E23" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>346000000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>364600000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>364600000</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>shares_yoy</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Share Count YoY %</t>
+        </is>
+      </c>
+      <c r="C24" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — one-glance summary (feeds the numbers sheet)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>400000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>452000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>471000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>491000000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>496000000</v>
+          <t>Auto from the other sheets. Flags are rough heuristics.</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>gross_margin_pct</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>63</v>
-      </c>
-      <c r="C3" t="n">
-        <v>62</v>
-      </c>
-      <c r="D3" t="n">
-        <v>61</v>
-      </c>
-      <c r="E3" t="n">
-        <v>59</v>
-      </c>
-      <c r="F3" t="n">
-        <v>58</v>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Example Corp</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>operating_margin_pct</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-12</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>net_income</t>
+          <t>Market cap</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-8000000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-25000000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-49000000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-70000000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-89000000</v>
+        <v>30700000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fcf</t>
+          <t>% from 52w high</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-2000000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-6000000</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-11000000</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-15000000</v>
+        <v>-29.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>shares_outstanding</t>
+          <t>Revenue (LTM)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>298000000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>315000000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>330000000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>346000000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>364600000</v>
+        <v>496000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>total_debt</t>
+          <t>Revenue 4y CAGR</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>900000000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1050000000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1350000000</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1450000000</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cash_and_equivalents</t>
+          <t>Gross margin (LTM)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>700000000</v>
-      </c>
-      <c r="C9" t="n">
-        <v>610000000</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Operating margin (LTM)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Net margin (LTM)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FCF (LTM)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-15000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FCF margin (LTM)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FCF yield</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ROIC (LTM)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Share count 4y CAGR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P/E (TTM)</t>
+        </is>
+      </c>
+      <c r="B18" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B19" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Quick flags</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Profitable? (LTM NI&gt;0)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FCF positive? (LTM)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Growing? (rev CAGR&gt;0)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Diluting? (share CAGR&gt;1%)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Over-levered? (ND/EBITDA&gt;3x)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — valuation &amp; bear/base/bull</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Inputs &amp; links</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>84.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LTM EPS</t>
+        </is>
+      </c>
+      <c r="B5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LTM FCF / share</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.041</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>(EPS)</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Exit multiple</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Implied price</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Upside %</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sales/sh</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-95.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sales/sh</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>520000000</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>465000000</v>
+        <v>8.16</v>
       </c>
       <c r="F9" t="n">
-        <v>410000000</v>
+        <v>-90.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sales/sh</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-80.59999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — peers (auto via PEERS(); optional / long-form)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Peer (auto)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Market Cap</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Rev Growth %</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Gross Mgn %</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Net Mgn %</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>FCF Yield %</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>NetDebt/EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Freightwave Systems Inc</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>142</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12400000000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
+      </c>
+      <c r="H5" t="n">
+        <v>71</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DepotOps Corp</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>63</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4100000000</v>
+      </c>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>62</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RouteLogic Holdings</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>208</v>
+      </c>
+      <c r="C7" t="n">
+        <v>28900000000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>76</v>
+      </c>
+      <c r="I7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CargoCloud Inc</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>58</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/company_data/dennis_data.xlsx
+++ b/fixtures/company_data/dennis_data.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -62,10 +65,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2729,7 +2733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2884,6 +2888,159 @@
       </c>
       <c r="F10" t="n">
         <v>-80.59999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WACC (auto — CAPM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Risk-free rate (10Y)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.043</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Equity risk premium</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Beta (5y)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.123</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.092</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Reverse DCF — growth priced into today's price</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Implied growth  (WACC − FCF/EV)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Historical FCF CAGR (4y)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Revenue CAGR (4y)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Priced-for − delivered (FCF)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>market prices in MORE growth than history delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Implied growth sensitivity (WACC ±1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WACC −1%</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WACC base</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WACC +1%</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.07099999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2897,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3112,6 +3269,415 @@
         <v>2.6</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DENNIS — self-scoring vs peers (percentile of THIS ticker in each peer column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PERCENTRANK.INC of the subject within the cleaned peer columns above. 'Read' bakes in direction so a glance tells you cheap/expensive and strong/weak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Percentile</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Higher is</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P/E (TTM)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>mid-pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mid-pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P/S (TTM)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>expensive vs peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rev growth % (3Y CAGR)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>71</v>
+      </c>
+      <c r="C17" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Net margin %</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FCF yield %</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>mid-pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Peer 3Y growth from revenue with date params; blank on refresh is harmless.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — recent news &amp; key developments (auto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Latest headlines (Date / Headline / Source / URL), spilled by the add-in. A news outlet as Source is fine — never a data-terminal brand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Headline</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Example Corp posts record quarterly revenue, tops estimates</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://example.com/news/record-revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Regulators open probe into logistics-software pricing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bloomberg</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://example.com/news/pricing-probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Example Corp unveils next-gen routing platform at expo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Associated Press</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://example.com/news/routing-platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://example.com/news/na-headline</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CEO outlines margin recovery and cost cuts in interview</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CNBC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://example.com/news/ceo-interview</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/fixtures/company_data/dennis_data.xlsx
+++ b/fixtures/company_data/dennis_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Peers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="News" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3054,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3097,27 +3097,77 @@
       </c>
       <c r="G4" s="1" t="inlineStr">
         <is>
-          <t>Rev Growth %</t>
+          <t>Gross Mgn %</t>
         </is>
       </c>
       <c r="H4" s="1" t="inlineStr">
         <is>
-          <t>Gross Mgn %</t>
+          <t>Net Mgn %</t>
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>Net Mgn %</t>
+          <t>FCF Yield %</t>
         </is>
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>FCF Yield %</t>
+          <t>NetDebt/EBITDA</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>NetDebt/EBITDA</t>
+          <t>Rev LTM (now)</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Rev LTM (-3Y)</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Rev Growth % (3Y CAGR)</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>cln P/E</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>cln EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>cln P/S</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>cln GrossM</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>cln NetM</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>cln FCFY</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>cln ND/EBITDA</t>
+        </is>
+      </c>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>cln RevGrw3Y</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3193,49 @@
         <v>9.1</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2037.36</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1240</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18.00000617793025</v>
+      </c>
+      <c r="N5" t="n">
+        <v>34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>71</v>
       </c>
-      <c r="I5" t="n">
+      <c r="R5" t="n">
         <v>6</v>
       </c>
-      <c r="J5" t="n">
+      <c r="S5" t="n">
         <v>2.1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="T5" t="n">
         <v>0.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18.00000617793025</v>
       </c>
     </row>
     <row r="6">
@@ -3180,19 +3260,47 @@
         <v>5.4</v>
       </c>
       <c r="G6" t="n">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="H6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1269.13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>980</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.000045233123721</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>41</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q6" t="n">
         <v>62</v>
       </c>
-      <c r="I6" t="n">
+      <c r="R6" t="n">
         <v>-4</v>
       </c>
-      <c r="J6" t="n">
+      <c r="S6" t="n">
         <v>0.6</v>
       </c>
-      <c r="K6" t="n">
+      <c r="T6" t="n">
         <v>1.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.000045233123721</v>
       </c>
     </row>
     <row r="7">
@@ -3217,19 +3325,49 @@
         <v>11.2</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3813.28</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21.99999146841334</v>
+      </c>
+      <c r="N7" t="n">
+        <v>41</v>
+      </c>
+      <c r="O7" t="n">
+        <v>26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q7" t="n">
         <v>76</v>
       </c>
-      <c r="I7" t="n">
+      <c r="R7" t="n">
         <v>12</v>
       </c>
-      <c r="J7" t="n">
+      <c r="S7" t="n">
         <v>3</v>
       </c>
-      <c r="K7" t="n">
+      <c r="T7" t="n">
         <v>0.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>21.99999146841334</v>
       </c>
     </row>
     <row r="8">
@@ -3254,19 +3392,43 @@
         <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="H8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>726.52</v>
+      </c>
+      <c r="L8" t="n">
+        <v>610</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6.000011672083172</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q8" t="n">
         <v>58</v>
       </c>
-      <c r="I8" t="n">
+      <c r="R8" t="n">
         <v>-22</v>
       </c>
-      <c r="J8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
         <v>2.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6.000011672083172</v>
       </c>
     </row>
     <row r="10">

--- a/fixtures/company_data/dennis_data.xlsx
+++ b/fixtures/company_data/dennis_data.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Snapshot" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Peers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="News" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshot" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1618,15 +1618,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Insider Ownership (%)</t>
+          <t>Insider Ownership (% of shares out)</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>0.08</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TR.InsiderPercentHeld</t>
+          <t>computed: L50 normalised — see the resolver at G47</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1644,15 +1644,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Institutional Own (%)</t>
+          <t>Institutional Own (% of shares out)</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>62</v>
+        <v>0.62</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TR.InstitutionsPercentHeld</t>
+          <t>computed: L51 normalised — see the resolver at G47</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3054,7 +3054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U22"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3476,6 +3476,26 @@
           <t>Read</t>
         </is>
       </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Peer low (p10)</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>Peer high (p90)</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>t (subject)</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>t (median)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3502,6 +3522,18 @@
           <t>mid-pack</t>
         </is>
       </c>
+      <c r="G13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>52</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5735</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3528,6 +3560,18 @@
           <t>mid-pack</t>
         </is>
       </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5909</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3554,6 +3598,18 @@
           <t>expensive vs peers</t>
         </is>
       </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1833</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5667</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3580,6 +3636,18 @@
           <t>strong vs peers</t>
         </is>
       </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4706</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3606,6 +3674,18 @@
           <t>strong vs peers</t>
         </is>
       </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8846000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5385</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3632,6 +3712,18 @@
           <t>strong vs peers</t>
         </is>
       </c>
+      <c r="G18" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.381</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3658,6 +3750,18 @@
           <t>strong vs peers</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3214</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3684,9 +3788,97 @@
           <t>mid-pack</t>
         </is>
       </c>
+      <c r="G20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5897</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>expensive vs peers</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7813</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4375</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
+        <is>
+          <t>Forward PEG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>cheap vs peers</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5294</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Peer 3Y growth from revenue with date params; blank on refresh is harmless.</t>
         </is>

--- a/fixtures/company_data/dennis_data.xlsx
+++ b/fixtures/company_data/dennis_data.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshot" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="History" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valuation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peers" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2465,260 +2466,815 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DENNIS — one-glance summary (feeds the numbers sheet)</t>
+          <t>DENNIS — quarterly results (8 quarters) — QoQ and YoY same quarter</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Auto from the other sheets. Flags are rough heuristics.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Example Corp</t>
+          <t>Both comparisons, never one. A retailer's Q4 beats its Q3 every year; only the YoY says whether anything moved.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>84.2</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>field_key</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Q1 FY-1</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Q2 FY-1</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Q3 FY-1</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Q4 FY-1</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Q1 FY-0</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Q2 FY-0</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>Q3 FY-0</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>Q4 FY-0</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Field mnemonic (verify)</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Market cap</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>30700000000</v>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>112000000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>121000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>114000000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>122000000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>141000000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>% from 52w high</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-29.83</v>
+          <t>gross_profit</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>66500000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>69700000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>71300000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>82000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>66599999.99999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>69200000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>70800000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>81200000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Revenue (LTM)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>496000000</v>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="F7" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>58</v>
+      </c>
+      <c r="J7" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Revenue 4y CAGR</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>5.5</v>
+          <t>operating_income</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-12000000</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-14000000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-15000000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-15000000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gross margin (LTM)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>58</v>
+          <t>operating_margin</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Operating Margin %</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-10.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-12.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-11.3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Operating margin (LTM)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-12</v>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-17000000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-19000000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-21000000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-22000000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-22000000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-24000000</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Net margin (LTM)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+          <t>net_margin</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>-14.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-18.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="I11" t="n">
         <v>-18</v>
+      </c>
+      <c r="J11" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FCF (LTM)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-15000000</v>
+          <t>operating_cf</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Operating Cash Flow</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-2000000</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FCF margin (LTM)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-3</v>
+          <t>capex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-700000</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-1400000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-1500000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1500000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-1600000</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FCF yield</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-5</v>
+          <t>fcf</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>-3700000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-3800000</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-2700000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-5400000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-4500000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4500000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-600000</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Net debt / EBITDA</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>9.800000000000001</v>
+          <t>fcf_margin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FCF Margin %</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ROIC (LTM)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-3.6</v>
+          <t>sbc</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Stock-Based Comp</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>22000000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="H16" t="n">
+        <v>27000000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share count 4y CAGR</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>5.2</v>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Cash &amp; Equivalents</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>505000000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>495000000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>465000000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>450000000</v>
+      </c>
+      <c r="H17" t="n">
+        <v>435000000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>422000000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>410000000</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P/E (TTM)</t>
-        </is>
-      </c>
-      <c r="B18" t="e">
-        <v>#N/A</v>
+          <t>total_debt</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1275000000</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1300000000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1325000000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1350000000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1375000000</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1400000000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1425000000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1450000000</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="B19" t="e">
-        <v>#N/A</v>
+          <t>net_debt</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>770000000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>805000000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>845000000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>885000000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>925000000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>965000000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1003000000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1040000000</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>Quick flags</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>total_equity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Total Equity</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1045000000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1040000000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1035000000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1030000000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1030000000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1032000000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1034000000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1036000000</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Profitable? (LTM NI&gt;0)</t>
+          <t>diluted_shares</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>Diluted Shares</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>338000000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>341000000</v>
+      </c>
+      <c r="E21" t="n">
+        <v>344000000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>346000000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>350000000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>355000000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>360000000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>364600000</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>computed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FCF positive? (LTM)</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Growing? (rev CAGR&gt;0)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Diluting? (share CAGR&gt;1%)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Over-levered? (ND/EBITDA&gt;3x)</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>EPS (diluted)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.062</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.061</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.066</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>computed</t>
         </is>
       </c>
     </row>
@@ -2733,27 +3289,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DENNIS — valuation &amp; bear/base/bull</t>
+          <t>DENNIS — one-glance summary (feeds the numbers sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Auto from the other sheets. Flags are rough heuristics.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Inputs &amp; links</t>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Example Corp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Current price</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2763,284 +3331,219 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTM EPS</t>
-        </is>
-      </c>
-      <c r="B5" t="e">
-        <v>#N/A</v>
+          <t>Market cap</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>30700000000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTM FCF / share</t>
+          <t>% from 52w high</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.041</v>
+        <v>-29.83</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>(EPS)</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Exit multiple</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Implied price</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Upside %</t>
-        </is>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Revenue (LTM)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>496000000</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bear</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Sales/sh</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-95.2</v>
+          <t>Revenue 4y CAGR</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sales/sh</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-90.3</v>
+          <t>Gross margin (LTM)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bull</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Sales/sh</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.32</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-80.59999999999999</v>
+          <t>Operating margin (LTM)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Net margin (LTM)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WACC (auto — CAPM)</t>
-        </is>
+          <t>FCF (LTM)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>-15000000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Risk-free rate (10Y)</t>
+          <t>FCF margin (LTM)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.043</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Equity risk premium</t>
+          <t>FCF yield</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Beta (5y)</t>
+          <t>Net debt / EBITDA</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cost of equity (Ke)</t>
+          <t>ROIC (LTM)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.123</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WACC</t>
+          <t>Share count 4y CAGR</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.092</v>
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P/E (TTM)</t>
+        </is>
+      </c>
+      <c r="B18" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Reverse DCF — growth priced into today's price</t>
-        </is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B19" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Implied growth  (WACC − FCF/EV)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.061</v>
-      </c>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Quick flags</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Historical FCF CAGR (4y)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.045</v>
+          <t>Profitable? (LTM NI&gt;0)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Revenue CAGR (4y)</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0.12</v>
+          <t>FCF positive? (LTM)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Priced-for − delivered (FCF)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>0.016</v>
+          <t>Growing? (rev CAGR&gt;0)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Diluting? (share CAGR&gt;1%)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>market prices in MORE growth than history delivered</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Implied growth sensitivity (WACC ±1%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>WACC −1%</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0.051</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>WACC base</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0.061</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>WACC +1%</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>0.07099999999999999</v>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Over-levered? (ND/EBITDA&gt;3x)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3054,834 +3557,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DENNIS — peers (auto via PEERS(); optional / long-form)</t>
+          <t>DENNIS — valuation &amp; bear/base/bull</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Inputs &amp; links</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Peer (auto)</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Market Cap</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>P/E</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>P/S</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>Gross Mgn %</t>
-        </is>
-      </c>
-      <c r="H4" s="1" t="inlineStr">
-        <is>
-          <t>Net Mgn %</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>FCF Yield %</t>
-        </is>
-      </c>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>NetDebt/EBITDA</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>Rev LTM (now)</t>
-        </is>
-      </c>
-      <c r="L4" s="1" t="inlineStr">
-        <is>
-          <t>Rev LTM (-3Y)</t>
-        </is>
-      </c>
-      <c r="M4" s="1" t="inlineStr">
-        <is>
-          <t>Rev Growth % (3Y CAGR)</t>
-        </is>
-      </c>
-      <c r="N4" s="1" t="inlineStr">
-        <is>
-          <t>cln P/E</t>
-        </is>
-      </c>
-      <c r="O4" s="1" t="inlineStr">
-        <is>
-          <t>cln EV/EBITDA</t>
-        </is>
-      </c>
-      <c r="P4" s="1" t="inlineStr">
-        <is>
-          <t>cln P/S</t>
-        </is>
-      </c>
-      <c r="Q4" s="1" t="inlineStr">
-        <is>
-          <t>cln GrossM</t>
-        </is>
-      </c>
-      <c r="R4" s="1" t="inlineStr">
-        <is>
-          <t>cln NetM</t>
-        </is>
-      </c>
-      <c r="S4" s="1" t="inlineStr">
-        <is>
-          <t>cln FCFY</t>
-        </is>
-      </c>
-      <c r="T4" s="1" t="inlineStr">
-        <is>
-          <t>cln ND/EBITDA</t>
-        </is>
-      </c>
-      <c r="U4" s="1" t="inlineStr">
-        <is>
-          <t>cln RevGrw3Y</t>
-        </is>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>84.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Freightwave Systems Inc</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>142</v>
-      </c>
-      <c r="C5" t="n">
-        <v>12400000000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>34</v>
-      </c>
-      <c r="E5" t="n">
-        <v>22</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>71</v>
-      </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2037.36</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1240</v>
-      </c>
-      <c r="M5" t="n">
-        <v>18.00000617793025</v>
-      </c>
-      <c r="N5" t="n">
-        <v>34</v>
-      </c>
-      <c r="O5" t="n">
-        <v>22</v>
-      </c>
-      <c r="P5" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>71</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>18.00000617793025</v>
+          <t>LTM EPS</t>
+        </is>
+      </c>
+      <c r="B5" t="e">
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DepotOps Corp</t>
+          <t>LTM FCF / share</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4100000000</v>
-      </c>
-      <c r="D6" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E6" t="n">
-        <v>41</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>62</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1269.13</v>
-      </c>
-      <c r="L6" t="n">
-        <v>980</v>
-      </c>
-      <c r="M6" t="n">
-        <v>9.000045233123721</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>41</v>
-      </c>
-      <c r="P6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>62</v>
-      </c>
-      <c r="R6" t="n">
-        <v>-4</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>9.000045233123721</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RouteLogic Holdings</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>208</v>
-      </c>
-      <c r="C7" t="n">
-        <v>28900000000</v>
-      </c>
-      <c r="D7" t="n">
-        <v>41</v>
-      </c>
-      <c r="E7" t="n">
-        <v>26</v>
-      </c>
-      <c r="F7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>76</v>
-      </c>
-      <c r="H7" t="n">
-        <v>12</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3813.28</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2100</v>
-      </c>
-      <c r="M7" t="n">
-        <v>21.99999146841334</v>
-      </c>
-      <c r="N7" t="n">
-        <v>41</v>
-      </c>
-      <c r="O7" t="n">
-        <v>26</v>
-      </c>
-      <c r="P7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>76</v>
-      </c>
-      <c r="R7" t="n">
-        <v>12</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>21.99999146841334</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>(EPS)</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Exit multiple</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Implied price</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Upside %</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CargoCloud Inc</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>19</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1800000000</v>
-      </c>
-      <c r="D8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E8" t="e">
-        <v>#N/A</v>
+          <t>Bear</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Sales/sh</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G8" t="n">
-        <v>58</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>726.52</v>
-      </c>
-      <c r="L8" t="n">
-        <v>610</v>
-      </c>
-      <c r="M8" t="n">
-        <v>6.000011672083172</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>58</v>
-      </c>
-      <c r="R8" t="n">
-        <v>-22</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6.000011672083172</v>
+        <v>-95.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sales/sh</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-90.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DENNIS — self-scoring vs peers (percentile of THIS ticker in each peer column)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>PERCENTRANK.INC of the subject within the cleaned peer columns above. 'Read' bakes in direction so a glance tells you cheap/expensive and strong/weak.</t>
-        </is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sales/sh</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.32</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-80.59999999999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>Subject</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>Percentile</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>Higher is</t>
-        </is>
-      </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>Peer low (p10)</t>
-        </is>
-      </c>
-      <c r="H12" s="1" t="inlineStr">
-        <is>
-          <t>Peer high (p90)</t>
-        </is>
-      </c>
-      <c r="I12" s="1" t="inlineStr">
-        <is>
-          <t>t (subject)</t>
-        </is>
-      </c>
-      <c r="J12" s="1" t="inlineStr">
-        <is>
-          <t>t (median)</t>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>WACC (auto — CAPM)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P/E (TTM)</t>
+          <t>Risk-free rate (10Y)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>worse (expensive/levered)</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>mid-pack</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>18</v>
-      </c>
-      <c r="H13" t="n">
-        <v>52</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.4706</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.5735</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EV/EBITDA</t>
+          <t>Equity risk premium</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
-      </c>
-      <c r="C14" t="n">
-        <v>24</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>worse (expensive/levered)</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>mid-pack</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>11</v>
-      </c>
-      <c r="H14" t="n">
-        <v>33</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.5909</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P/S (TTM)</t>
+          <t>Beta (5y)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>worse (expensive/levered)</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>expensive vs peers</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>8</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.1833</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.5667</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Rev growth % (3Y CAGR)</t>
+          <t>Cost of equity (Ke)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
-      </c>
-      <c r="C16" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>strong vs peers</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>21</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.8235</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.4706</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>WACC</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71</v>
-      </c>
-      <c r="C17" t="n">
-        <v>62</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>strong vs peers</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>48</v>
-      </c>
-      <c r="H17" t="n">
-        <v>74</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.8846000000000001</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.5385</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Net margin %</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>strong vs peers</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>-12</v>
-      </c>
-      <c r="H18" t="n">
-        <v>9</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.8571</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.381</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FCF yield %</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>better</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>strong vs peers</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.6429</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.3214</v>
+          <t>Reverse DCF — growth priced into today's price</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Net debt / EBITDA</t>
+          <t>Implied growth  (WACC − FCF/EV)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>worse (expensive/levered)</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>mid-pack</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.5897</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Forward P/E</t>
+          <t>Historical FCF CAGR (4y)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="C21" t="n">
-        <v>21</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>worse (expensive/levered)</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>expensive vs peers</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>14</v>
-      </c>
-      <c r="H21" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.7813</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.4375</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Forward PEG</t>
+          <t>Revenue CAGR (4y)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>worse (expensive/levered)</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>cheap vs peers</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.2353</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.5294</v>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Priced-for − delivered (FCF)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.016</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Peer 3Y growth from revenue with date params; blank on refresh is harmless.</t>
-        </is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>market prices in MORE growth than history delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Implied growth sensitivity (WACC ±1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WACC −1%</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WACC base</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.061</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WACC +1%</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.07099999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -3895,6 +3878,847 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:U24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>DENNIS — peers (auto via PEERS(); optional / long-form)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Peer (auto)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Market Cap</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>P/E</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>P/S</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Gross Mgn %</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>Net Mgn %</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>FCF Yield %</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>NetDebt/EBITDA</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>Rev LTM (now)</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>Rev LTM (-3Y)</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>Rev Growth % (3Y CAGR)</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>cln P/E</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>cln EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>cln P/S</t>
+        </is>
+      </c>
+      <c r="Q4" s="1" t="inlineStr">
+        <is>
+          <t>cln GrossM</t>
+        </is>
+      </c>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>cln NetM</t>
+        </is>
+      </c>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>cln FCFY</t>
+        </is>
+      </c>
+      <c r="T4" s="1" t="inlineStr">
+        <is>
+          <t>cln ND/EBITDA</t>
+        </is>
+      </c>
+      <c r="U4" s="1" t="inlineStr">
+        <is>
+          <t>cln RevGrw3Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Freightwave Systems Inc</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>142</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12400000000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>71</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2037.36</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1240</v>
+      </c>
+      <c r="M5" t="n">
+        <v>18.00000617793025</v>
+      </c>
+      <c r="N5" t="n">
+        <v>34</v>
+      </c>
+      <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>71</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18.00000617793025</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DepotOps Corp</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>63</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4100000000</v>
+      </c>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>62</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1269.13</v>
+      </c>
+      <c r="L6" t="n">
+        <v>980</v>
+      </c>
+      <c r="M6" t="n">
+        <v>9.000045233123721</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>41</v>
+      </c>
+      <c r="P6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>62</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.000045233123721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RouteLogic Holdings</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>208</v>
+      </c>
+      <c r="C7" t="n">
+        <v>28900000000</v>
+      </c>
+      <c r="D7" t="n">
+        <v>41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>26</v>
+      </c>
+      <c r="F7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>76</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3813.28</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2100</v>
+      </c>
+      <c r="M7" t="n">
+        <v>21.99999146841334</v>
+      </c>
+      <c r="N7" t="n">
+        <v>41</v>
+      </c>
+      <c r="O7" t="n">
+        <v>26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>76</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>21.99999146841334</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CargoCloud Inc</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1800000000</v>
+      </c>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>58</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>726.52</v>
+      </c>
+      <c r="L8" t="n">
+        <v>610</v>
+      </c>
+      <c r="M8" t="n">
+        <v>6.000011672083172</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>58</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-22</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6.000011672083172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DENNIS — self-scoring vs peers (percentile of THIS ticker in each peer column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PERCENTRANK.INC of the subject within the cleaned peer columns above. 'Read' bakes in direction so a glance tells you cheap/expensive and strong/weak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>Subject</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>Percentile</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>Higher is</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t>Peer low (p10)</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>Peer high (p90)</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t>t (subject)</t>
+        </is>
+      </c>
+      <c r="J12" s="1" t="inlineStr">
+        <is>
+          <t>t (median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P/E (TTM)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>mid-pack</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>52</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>22</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>mid-pack</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" t="n">
+        <v>33</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.5909</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P/S (TTM)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>expensive vs peers</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.1833</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5667</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Rev growth % (3Y CAGR)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" t="n">
+        <v>21</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8235</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.4706</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>71</v>
+      </c>
+      <c r="C17" t="n">
+        <v>62</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>48</v>
+      </c>
+      <c r="H17" t="n">
+        <v>74</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8846000000000001</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5385</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Net margin %</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>-12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.381</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FCF yield %</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>strong vs peers</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6429</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.3214</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>mid-pack</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2308</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.5897</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>expensive vs peers</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7813</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4375</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Forward PEG</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>worse (expensive/levered)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>cheap vs peers</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2353</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.5294</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Peer 3Y growth from revenue with date params; blank on refresh is harmless.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
